--- a/data/eda/eda_results.xlsx
+++ b/data/eda/eda_results.xlsx
@@ -15,6 +15,14 @@
     <sheet name="LandTitle_Freq" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="PropertyType_Freq" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Categorical_MajorSplits" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="CoreCorr_Matrix" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CoreCorr_vs_Price" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="AmenityCorr_vs_Price" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="PropSize_FilterSummary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="PropSize_LinearFit" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="MedianPrice_Bedroom" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="MedianPrice_Bathroom" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="MedianPrice_Parking" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,6 +508,698 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Correlation_with_log10_price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Property Size</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6255872406665152</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.5374563690667684</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Parking Lot</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5354072317067599</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Listed_Facility_Count</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.4453560062421968</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t># of Floors</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.4334338006095494</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2803238629330735</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Is_Non_Bumi_Lot</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2224453805251474</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Freehold Indicator</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1674479759714746</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Floor_Range_Ordinal</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1216846122333563</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Units</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.1431114588118842</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Property Age</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.2860957303181567</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Amenity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Correlation_with_log10_price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Has_Gymnasium</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.4886508530798196</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Has_Swimming_Pool</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.4723588827079984</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Has_Security</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3697951895584869</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Has_Sauna</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3615654049173069</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Has_Barbeque_Area</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.3383663635583544</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Has_Lift</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.294116997599752</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Has_Playground</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2800053843493329</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Has_Multipurpose_Hall</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2730776849789968</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Has_Parking</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2516058507134744</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Has_Squash_Court</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2431689004328367</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Has_Jogging_Track</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2109885327460077</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Has_Club_House</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2045927980161593</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Has_Tennis_Court</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.202129361478666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Has_Mall</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.06321624950007881</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Has_Minimart</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.04603767131185886</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Has_Railway_Station</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.04273667686706733</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Has_Hospital</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.02166810316346984</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Has_Bus_Stop</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.01112527278084855</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Has_Park</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.00316203991299378</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Has_Highway</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.003238283556783943</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Has_School</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.02076750056887783</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total rows</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Size limit (sqft)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Price limit (RM)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rows excluded</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pct excluded</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Slope</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>507.2685927140838</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-89177.87370262251</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pearson r (filtered subset)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6984243625194128</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bedroom_Group4</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Median_Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>299000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>339500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>590000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bathroom_Group</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Median_Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Parking_Group</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Median_Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>512500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3+</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1163,4 +1863,601 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Property Size</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t># of Floors</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Total Units</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Parking Lot</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Property Age</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Listed_Facility_Count</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Floor_Range_Ordinal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Is_Non_Bumi_Lot</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Freehold Indicator</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>log10_price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6415932923101386</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5288652372547497</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.08185245947439446</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.06751630272877933</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.290232455456434</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1151032035362746</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.06565020318969297</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.002549291935035446</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.03809033945521575</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.04335729528220953</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2803238629330735</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6415932923101386</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6949750885440661</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.06750749730216192</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.109944794582851</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4132271122017381</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.02889918993268391</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2145804625563927</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.06713073919489604</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.06957571287133131</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.08877045986706047</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5374563690667684</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Property Size</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5288652372547497</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6949750885440661</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.08025616529532145</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.1448967038780753</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4629307921156183</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.06931410585096399</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.236811972153411</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.08818412378571353</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.08063724909653158</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.07661906821681265</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6255872406665152</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t># of Floors</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.08185245947439446</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.06750749730216192</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08025616529532145</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.27685467213794</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2990099749530841</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.4941474555326409</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3487036486018398</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2138989644410152</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2013136859700276</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1135237482754659</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4334338006095494</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Units</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.06751630272877933</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.109944794582851</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1448967038780753</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.27685467213794</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.01796998105249136</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.23285931742557</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.02071037033466134</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01339503620357464</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.003763591529466998</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.07145489174100032</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.1431114588118842</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Parking Lot</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.290232455456434</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4132271122017381</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4629307921156183</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2990099749530841</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.01796998105249136</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.3895305814462905</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2758643530836735</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1458029217477177</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1282860544198766</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.139639582451698</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5354072317067599</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Property Age</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1151032035362746</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.02889918993268391</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06931410585096399</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.4941474555326409</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.23285931742557</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.3895305814462905</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.198710461726199</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.1771725377369777</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.04913167254152655</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.03966896998309878</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.2860957303181567</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Listed_Facility_Count</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.06565020318969297</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2145804625563927</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.236811972153411</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3487036486018398</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02071037033466134</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2758643530836735</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.198710461726199</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1108159202576194</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.09708277179777847</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1146672987311425</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4453560062421968</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Floor_Range_Ordinal</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.002549291935035446</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.06713073919489604</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.08818412378571353</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2138989644410152</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01339503620357464</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1458029217477177</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1771725377369777</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1108159202576194</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.04330613115612112</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03835346913064037</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1216846122333563</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Is_Non_Bumi_Lot</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.03809033945521575</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.06957571287133131</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.08063724909653158</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2013136859700276</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.003763591529466998</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1282860544198766</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.04913167254152655</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.09708277179777847</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.04330613115612112</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2192213266938334</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2224453805251474</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Freehold Indicator</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.04335729528220953</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.08877045986706047</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.07661906821681265</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1135237482754659</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.07145489174100032</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.139639582451698</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.03966896998309878</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1146672987311425</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.03835346913064037</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2192213266938334</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1674479759714746</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>log10_price</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2803238629330735</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5374563690667684</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6255872406665152</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4334338006095494</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1431114588118842</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5354072317067599</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2860957303181567</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4453560062421968</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1216846122333563</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2224453805251474</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1674479759714746</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>